--- a/data/numeric/input/data_147/314班第一次摸底考.xlsx
+++ b/data/numeric/input/data_147/314班第一次摸底考.xlsx
@@ -2885,13 +2885,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C29CC9A-F927-40CA-8B41-0CEE268C2888}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46DE96ED-27E7-4F61-B76C-69FD1DDE815F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D4BCACC-CA45-4B71-AD58-0894CC1EC6EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{114F968B-2D86-4656-8BC0-487D4CA976D7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35F2293B-6266-4C17-9D21-661C89295734}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D079592E-B2E3-475B-B00E-4DACCA20365F}"/>
 </file>